--- a/data/AI财富专家内测/证券0820测评功能.xlsx
+++ b/data/AI财富专家内测/证券0820测评功能.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20752" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 " sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="补充问题" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="评测结论" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1 " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充问题" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评测结论" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -204,6 +204,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="35">
@@ -682,7 +688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -720,6 +726,7 @@
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1797,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="9" min="1" max="1"/>
@@ -1852,7 +1859,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="9">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>说明</t>
@@ -1861,10 +1868,25 @@
       <c r="B5" s="10" t="inlineStr">
         <is>
           <t>评分由 5 分基础扣除 2 分得到；证据图片均使用项目内归档资源，账户金额截图已脱敏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" s="9">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HTML测试报告</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>https://littlemo.github.io/pingan_app_use_report/?version=ai-wealth&amp;v=20260830-1</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/AI财富专家内测/证券0820测评功能.xlsx
+++ b/data/AI财富专家内测/证券0820测评功能.xlsx
@@ -1612,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="9">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>问题7</t>
@@ -1788,6 +1788,90 @@
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" s="9">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>问题8</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>模型对话Bug</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>回复开场白重复输出，内容拼接缺少整体润色</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>针对白酒市场行情及相关 ETF 的提问，回复中“您好，我是您的财富专家”被重复输出两次；两段内容直接拼接，前后衔接割裂，疑似不同提示词输出合并后未进行统一文案调整。</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>同一条回复中开场白只出现一次；多段生成内容合并后应进行统一去重、排序和语义衔接。</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>对多段提示词输出结果增加统一的文案后处理，去除重复开场白并优化段落衔接。</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>imgs/ai-wealth/ai-wealth-duplicate-greeting.png</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" s="9">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>问题9</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>功能逻辑 Bug</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>ETF 实时折溢价率取值错误导致分析结论失真</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>在请求寻找折价率较高的 ETF 场景中，回复表格内多只 ETF 的实时折溢价率均展示为 0.00%，但实际基金详情页显示折价率并非 0，例如恒生医疗 ETF 嘉实实时折价率为 -1.10%。下方关于折价幅度和产品排序的分析也基于错误的 0.00% 数据。</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>回复表格应准确展示各 ETF 的实时折溢价率，并基于最新、真实的数据进行筛选、排序和分析；无法获取实时数据时应明确提示。</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>核对实时折溢价率数据接口、字段映射和计算逻辑，避免使用默认 0 覆盖真实值；当数据异常时阻断后续分析并提示用户。</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>imgs/ai-wealth/ai-wealth-etf-discount-rate-zero-01.png; imgs/ai-wealth/ai-wealth-etf-discount-rate-zero-02.png; imgs/ai-wealth/ai-wealth-etf-discount-rate-detail-reference.png</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1843,7 +1927,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1939,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>UI交互优化 3 条；功能逻辑 Bug 2 条；模型对话Bug 2 条</t>
+          <t>UI交互优化 3 条；功能逻辑 Bug 3 条；模型对话Bug 3 条</t>
         </is>
       </c>
     </row>
@@ -1872,14 +1956,14 @@
       </c>
     </row>
     <row r="6" s="9">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>HTML测试报告</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://littlemo.github.io/pingan_app_use_report/?version=ai-wealth&amp;v=20260830-1</t>
+          <t>https://littlemo.github.io/pingan_app_use_report/?version=ai-wealth&amp;v=20260901-2</t>
         </is>
       </c>
     </row>

--- a/data/AI财富专家内测/证券0820测评功能.xlsx
+++ b/data/AI财富专家内测/证券0820测评功能.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://littlemo.github.io/pingan_app_use_report/?version=ai-wealth&amp;v=20260901-2</t>
+          <t>https://littlemo.github.io/pingan_app_use_report/?version=ai-wealth&amp;v=20260901-3</t>
         </is>
       </c>
     </row>
